--- a/Config/Excel/CardTipConfig.xlsx
+++ b/Config/Excel/CardTipConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -92,6 +92,12 @@
   </si>
   <si>
     <t>不可以与任意牌连接，只能单独拖动</t>
+  </si>
+  <si>
+    <t>无花色</t>
+  </si>
+  <si>
+    <t>不参与任意花色判断</t>
   </si>
 </sst>
 </file>
@@ -1247,8 +1253,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="18.3333333333333" customWidth="1"/>
@@ -1362,6 +1368,20 @@
         <v>18</v>
       </c>
     </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>106</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:B8" etc:filterBottomFollowUsedRange="0">
     <extLst/>

--- a/Config/Excel/CardTipConfig.xlsx
+++ b/Config/Excel/CardTipConfig.xlsx
@@ -58,40 +58,40 @@
     <t>描述</t>
   </si>
   <si>
+    <t>多重点数</t>
+  </si>
+  <si>
+    <t>可以用其中一点数进行连接</t>
+  </si>
+  <si>
+    <t>点数-1</t>
+  </si>
+  <si>
+    <t>任意放下</t>
+  </si>
+  <si>
+    <t>可以放在任意牌上</t>
+  </si>
+  <si>
+    <t>点数-2</t>
+  </si>
+  <si>
+    <t>蜘蛛</t>
+  </si>
+  <si>
+    <t>可以作为任意点数连接，花色需要相同</t>
+  </si>
+  <si>
+    <t>无点数</t>
+  </si>
+  <si>
+    <t>不可以与任意牌连接，只能单独拖动</t>
+  </si>
+  <si>
     <t>多重花色</t>
   </si>
   <si>
     <t>可以用其中一花色进行连接</t>
-  </si>
-  <si>
-    <t>多重点数</t>
-  </si>
-  <si>
-    <t>可以用其中一点数进行连接</t>
-  </si>
-  <si>
-    <t>点数-1</t>
-  </si>
-  <si>
-    <t>任意放下</t>
-  </si>
-  <si>
-    <t>可以放在任意牌上</t>
-  </si>
-  <si>
-    <t>点数-2</t>
-  </si>
-  <si>
-    <t>蜘蛛</t>
-  </si>
-  <si>
-    <t>可以作为任意点数连接，花色需要相同</t>
-  </si>
-  <si>
-    <t>无点数</t>
-  </si>
-  <si>
-    <t>不可以与任意牌连接，只能单独拖动</t>
   </si>
   <si>
     <t>无花色</t>
@@ -1320,10 +1320,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1331,13 +1331,13 @@
         <v>103</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1345,7 +1345,7 @@
         <v>104</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>105</v>
+        <v>201</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>106</v>
+        <v>202</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
